--- a/validation_1990_age8/edge_validation.xlsx
+++ b/validation_1990_age8/edge_validation.xlsx
@@ -146,22 +146,24 @@
       </c>
       <c r="F2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">The blinded family study finds excess ADD among first-degree relatives after accounting for several measured factors. This adds family-genetic evidence, but does not isolate inherited effects from shared environment or establish the claim that genetic liability contributes strongly at exactly age eight.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Retain familial/genetic liability as a qualified pathway; avoid a quantified strong genetic effect from family-history evidence alone.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2387786: These results confirm and extend previous findings indicating important family-genetic risk factors in ADD.
+Location: Family-genetic and psychosocial risk factors in DSM-III attention deficit disorder - PubMed.html; English abstract (#eng-abstract)
+Relevance: Blinded family study supports familial liability; shared environment is not fully separated and strong genetic causation or an exact-age effect is not established.</t>
         </is>
       </c>
     </row>
@@ -391,7 +393,7 @@
       </c>
       <c r="G7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr" s="0">
@@ -438,7 +440,7 @@
       </c>
       <c r="G8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="0">
@@ -485,7 +487,7 @@
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="0">
@@ -532,7 +534,7 @@
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="0">
@@ -631,7 +633,7 @@
       </c>
       <c r="G12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr" s="0">
@@ -678,7 +680,7 @@
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr" s="0">
@@ -725,7 +727,7 @@
       </c>
       <c r="G14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="0">
@@ -772,7 +774,7 @@
       </c>
       <c r="G15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr" s="0">
@@ -819,7 +821,7 @@
       </c>
       <c r="G16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="0">
@@ -866,17 +868,19 @@
       </c>
       <c r="G17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">Parent–teacher diagnostic concordance does not measure teacher referral causing parental awareness. No added abstract establishes that direction or mechanism.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Retain as unvalidated; obtain temporal evidence on school-to-parent recognition.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2228921: there was a 90% probability that the teacher report would result in a positive diagnosis given a positive parent diagnosis
+Location: Parent-based diagnosis of attention deficit disorder predicts a diagnosis based on teacher report - PubMed.html; English abstract (#eng-abstract)
+Relevance: Diagnostic concordance among 43 clinically referred children aged 4–17 supports parent information in assessment; parental awareness was not manipulated and referral-population prediction is not a causal estimate.</t>
         </is>
       </c>
     </row>
@@ -913,7 +917,7 @@
       </c>
       <c r="G18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="0">
@@ -960,7 +964,7 @@
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="0">
@@ -1007,7 +1011,7 @@
       </c>
       <c r="G20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr" s="0">
@@ -1103,7 +1107,7 @@
       </c>
       <c r="G22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="0">
@@ -1150,7 +1154,7 @@
       </c>
       <c r="G23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr" s="0">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="G24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="0">
@@ -1239,22 +1243,24 @@
       </c>
       <c r="F25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">Parent-based diagnosis was corroborated by teacher report in a clinically referred pediatric sample. This supports a narrower parent-information-to-assessment pathway, not a causal effect of parental awareness on diagnosis likelihood.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Describe parent information as an assessment input; do not interpret diagnostic concordance as an intervention on awareness.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2228921: there was a 90% probability that the teacher report would result in a positive diagnosis given a positive parent diagnosis
+Location: Parent-based diagnosis of attention deficit disorder predicts a diagnosis based on teacher report - PubMed.html; English abstract (#eng-abstract)
+Relevance: Diagnostic concordance among 43 clinically referred children aged 4–17 supports parent information in assessment; parental awareness was not manipulated and referral-population prediction is not a causal estimate.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1297,7 @@
       </c>
       <c r="G26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr" s="0">
@@ -1338,7 +1344,7 @@
       </c>
       <c r="G27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr" s="0">
@@ -1385,7 +1391,7 @@
       </c>
       <c r="G28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="0">
@@ -1432,7 +1438,7 @@
       </c>
       <c r="G29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr" s="0">
@@ -1479,7 +1485,7 @@
       </c>
       <c r="G30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr" s="0">
@@ -1526,7 +1532,7 @@
       </c>
       <c r="G31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="0">
@@ -1573,7 +1579,7 @@
       </c>
       <c r="G32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="0">
@@ -1620,7 +1626,7 @@
       </c>
       <c r="G33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="0">
@@ -1667,7 +1673,7 @@
       </c>
       <c r="G34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr" s="0">
@@ -1714,7 +1720,7 @@
       </c>
       <c r="G35" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr" s="0">
@@ -1761,7 +1767,7 @@
       </c>
       <c r="G36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr" s="0">
@@ -1808,17 +1814,19 @@
       </c>
       <c r="G37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">The diagnostic-criteria critique discusses limitations and possible improvements, but does not estimate whether misdiagnosis reduces accurate identification in the age-eight population.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Retain as unvalidated; define accurate diagnosis and measure diagnostic errors.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2289969: The implications of these revisions for clinical diagnosis are also discussed.
+Location: A critique of current diagnostic criteria for attention deficit hyperactivity disorder_ clinical and research implications - PubMed.html; English abstract (#eng-abstract)
+Relevance: Criteria discussion is not an error-rate or causal diagnostic study.</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1863,7 @@
       </c>
       <c r="G38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr" s="0">
@@ -1902,7 +1910,7 @@
       </c>
       <c r="G39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr" s="0">
@@ -1996,22 +2004,27 @@
       </c>
       <c r="F41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">The review recommends behavioral intervention in ADHD care, and two diagnosed preschool families received parent training. This supports a clinical diagnosis-to-behavioral-care pathway, not a real-world access probability or an age-eight-specific referral effect.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Retain as a qualified care pathway; identify parent training and the younger case-study population.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_1974836: For maximum impact, pharmacotherapy should be accompanied by behavioral, educational, and psychosocial intervention.
+Location: Attention-deficit hyperactivity disorder - PubMed.html; English abstract (#eng-abstract)
+Relevance: Clinical review recommendation; not a controlled behavioral-treatment or school-accommodation outcome study.
+PMID_2273073: Improvements were found in parents' confidence in their child management ability and knowledge of behavioral principles, in certain child behavior problems, in parental ratings of hyperactivity, and in the parent-child relationship.
+Location: The effects of behavioral parent training on families with young hyperactive children - PubMed.html; English abstract (#eng-abstract)
+Relevance: Two uncontrolled preschool family case studies; narrow and younger than age eight, with no independent treatment-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2061,7 @@
       </c>
       <c r="G42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr" s="0">
@@ -2095,7 +2108,7 @@
       </c>
       <c r="G43" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr" s="0">
@@ -2142,7 +2155,7 @@
       </c>
       <c r="G44" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr" s="0">
@@ -2189,7 +2202,7 @@
       </c>
       <c r="G45" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr" s="0">
@@ -2236,7 +2249,7 @@
       </c>
       <c r="G46" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr" s="0">
@@ -2283,7 +2296,7 @@
       </c>
       <c r="G47" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr" s="0">
@@ -2330,7 +2343,7 @@
       </c>
       <c r="G48" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr" s="0">
@@ -2372,22 +2385,27 @@
       </c>
       <c r="F49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">Two preschool family case studies reported improved child behavior and parent-child relationships after parent training. The evidence is uncontrolled and younger than age eight; it supports only part of the broad classroom/home impairment claim.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Specify parent training and limited home/family outcomes; obtain controlled school-age evidence before asserting a general causal effect.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2273073: Improvements were found in parents' confidence in their child management ability and knowledge of behavioral principles, in certain child behavior problems, in parental ratings of hyperactivity, and in the parent-child relationship.
+Location: The effects of behavioral parent training on families with young hyperactive children - PubMed.html; English abstract (#eng-abstract)
+Relevance: Two uncontrolled preschool family case studies; narrow and younger than age eight, with no independent treatment-effect estimate.
+PMID_1974836: For maximum impact, pharmacotherapy should be accompanied by behavioral, educational, and psychosocial intervention.
+Location: Attention-deficit hyperactivity disorder - PubMed.html; English abstract (#eng-abstract)
+Relevance: Clinical review recommendation; not a controlled behavioral-treatment or school-accommodation outcome study.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2442,7 @@
       </c>
       <c r="G50" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr" s="0">
@@ -2471,12 +2489,12 @@
       </c>
       <c r="G51" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Methylphenidate improved a reaction-time measure in ages 7-12 and reduced rated symptoms in adolescents. The age-eight and broad symptom-severity claim is only partly covered.</t>
+          <t xml:space="preserve">Existing controlled PDF trials are supplemented by a methylphenidate crossover trial in boys aged 7.8–9.9 with improved attention during baseball, and a double-blind school trial with reduced disruptive and off-task behavior. The negative direction is better supported, but evidence remains medication-, domain-, and sample-specific rather than an exact-age estimate of overall severity.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain the negative edge, specifying methylphenidate, measured outcome, and age range.</t>
+          <t xml:space="preserve">Retain the negative edge with methylphenidate and measured attention/behavior outcomes; do not generalize to every medication or symptom domain.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr" s="0">
@@ -2486,7 +2504,16 @@
 Relevance: Ages 7.0-12.4 in a double-blind drug-placebo design; the outcome is reaction time, narrower than overall symptom severity.
 ADOLESCENT_MPH: Methylphenidate significantly reduced teachers' and parents' ratings of hyperactivity, inattention, and oppositionality.
 Location: PDF page 1
-Relevance: Controlled trial supports symptom reduction in ages 12-18, not specifically age eight or adults.</t>
+Relevance: Controlled trial supports symptom reduction in ages 12-18, not specifically age eight or adults.
+PMID_2319047: The effects of 0.3 and 0.6 mg/kg methylphenidate were analyzed in a double-blind, placebo-controlled, cross-over study in which 17 boys (ages 7.8-9.9 years) with attention deficit hyperactivity disorder (ADHD) played in baseball games.
+Location: Methylphenidate and baseball playing in ADHD children_ who's on first_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Age range includes eight; randomized-condition comparison addresses attention during a specific activity, not all impairment or all medications.
+PMID_2319047: Results revealed that methylphenidate had a beneficial effect on attending during the game.
+Location: Methylphenidate and baseball playing in ADHD children_ who's on first_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Improved attention in baseball supplies narrower functional-context evidence for children near eight.
+PMID_2228923: In the classroom, both doses of methylphenidate also resulted in reduced levels of motor movement, off-task behavior, noncompliance, and disruptiveness.
+Location: Methylphenidate in aggressive-hyperactive boys_ I. Effects on peer aggression in public school settings - PubMed.html; English abstract (#eng-abstract)
+Relevance: Double-blind trial in 11 aggressive-hyperactive children; specific classroom outcomes, age range unspecified in abstract, parent ratings did not mirror teacher ratings.</t>
         </is>
       </c>
     </row>
@@ -2518,22 +2545,30 @@
       </c>
       <c r="F52" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">Placebo-controlled methylphenidate studies show better attention during baseball, classroom behavior, and work output in selected child populations. Some learning and social outcomes did not improve. These are narrower functional gains, not a universal reduction in childhood impairment.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Retain as domain-specific benefit; distinguish classroom/on-task gains from learning, social functioning, and global impairment.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2319047: Results revealed that methylphenidate had a beneficial effect on attending during the game.
+Location: Methylphenidate and baseball playing in ADHD children_ who's on first_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Improved attention in baseball supplies narrower functional-context evidence for children near eight.
+PMID_2228923: In the classroom, both doses of methylphenidate also resulted in reduced levels of motor movement, off-task behavior, noncompliance, and disruptiveness.
+Location: Methylphenidate in aggressive-hyperactive boys_ I. Effects on peer aggression in public school settings - PubMed.html; English abstract (#eng-abstract)
+Relevance: Double-blind trial in 11 aggressive-hyperactive children; specific classroom outcomes, age range unspecified in abstract, parent ratings did not mirror teacher ratings.
+PMID_2135682: Significant increases in work output, on-task behavior, and attentional skills were associated with methylphenidate.
+Location: Efficacy of methylphenidate among mentally retarded children with attention deficit hyperactivity disorder - PubMed.html; English abstract (#eng-abstract)
+Relevance: Double-blind crossover in 12 children with IQ 50–74; learning and free-play social interaction did not significantly improve, limiting global impairment claims.</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2652,7 @@
       </c>
       <c r="G54" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr" s="0">
@@ -2664,19 +2699,22 @@
       </c>
       <c r="G55" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The adolescent trial directly reports mild side effects and weight reduction, but does not provide age-eight adverse-event evidence.</t>
+          <t xml:space="preserve">A triple-blind pediatric crossover trial directly reports increased appetite, sleep, stomachache and headache side effects versus placebo, strengthening the existing adolescent evidence. Exact age-eight results are not supplied, and many reported behaviors also occurred under placebo.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain with drug and adolescent age scope; add child-specific adverse-event evidence.</t>
+          <t xml:space="preserve">Retain drug-specific adverse-effect support; report generally mild severity and avoid attributing every observed behavior to medication.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ADOLESCENT_MPH: Stimulant treatment produced mild side effects and weight reduction.
 Location: PDF page 1
-Relevance: Direct treatment adverse-effect evidence in adolescents.</t>
+Relevance: Direct treatment adverse-effect evidence in adolescents.
+PMID_2196520: Parent ratings indicated that only the side effects of decreased appetite, insomnia, stomachaches, and headaches increased significantly in frequency and severity during the two active medication doses as compared with the placebo condition.
+Location: Side effects of methylphenidate in children with attention deficit hyperactivity disorder_ a systemic, placebo-controlled evaluation - PubMed.html; English abstract (#eng-abstract)
+Relevance: Triple-blind crossover in 83 children supplies direct pediatric adverse-effect evidence; exact age-eight estimate is unavailable and most adverse effects were mild.</t>
         </is>
       </c>
     </row>
@@ -2708,22 +2746,24 @@
       </c>
       <c r="F56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">The pediatric side-effect trial reports immediate medication discontinuation for serious adverse effects in three children. This supports reduced treatment continuation, a narrower endpoint than voluntary adherence or a general dose-taking measure.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant pediatric evidence.</t>
+          <t xml:space="preserve">Specify adverse-effect-related discontinuation; distinguish supervised stopping from nonadherence.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2196520: Three children (3.6%) had side effects that were sufficiently serious to warrant immediate discontinuation of medication.
+Location: Side effects of methylphenidate in children with attention deficit hyperactivity disorder_ a systemic, placebo-controlled evaluation - PubMed.html; English abstract (#eng-abstract)
+Relevance: Direct adverse-effect-to-discontinuation evidence; clinician-directed stopping is narrower than voluntary adherence, with exact ages unspecified.</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2800,7 @@
       </c>
       <c r="G57" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr" s="0">
@@ -2807,7 +2847,7 @@
       </c>
       <c r="G58" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr" s="0">
@@ -2854,7 +2894,7 @@
       </c>
       <c r="G59" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 1990 paper directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
+          <t xml:space="preserve">No supplied 1990 PDF or HTML abstract directly establishes this edge's direction, sign, and stated mechanism for children around age eight.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr" s="0">
@@ -2895,7 +2935,7 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Local PDF</t>
+          <t xml:space="preserve">Local file (PDF or HTML)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
@@ -2992,8 +3032,558 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2365665</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">A controlled family history study of Tourette's syndrome, I: Attention-deficit hyperactivity disorder and learning disorders</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/A controlled family history study of Tourette's syndrome, I_ Attention-deficit hyperactivity disorder and learning disorders - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f1f94444f29b5f4673d64acee9d8dcbaf18da10e56b066793e5dd3676018a7bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2289969</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">A critique of current diagnostic criteria for attention deficit hyperactivity disorder: clinical and research implications</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/A critique of current diagnostic criteria for attention deficit hyperactivity disorder_ clinical and research implications - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">218fa32e8a4442796da8f6c55a17d15e743e957e8d002ce7fa4a2fc0018443d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2251528</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention deficit hyperactivity disorder: does it affect adults too?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f3c844fb24bcf8b0335fd6d1b65ca7f21b316162d3a61e019c07cd2948437bf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2326123</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention of hyperactive preschool children--electrodermal activity during auditory stimulation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Attention of hyperactive preschool children--electrodermal activity during auditory stimulation - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">07f5dfbb51849ed390b387078315db9696fcdce856322782bcf9f5638d00f7f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_1974836</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention-deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Attention-deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">d8c2c33f0b989dcc71433445922ae7b78df77d6db60b44b52f1e60fa2d02e075</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2228924</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Effects of methylphenidate on adolescents with aggressive conduct disorder and ADDH: a preliminary report</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Effects of methylphenidate on adolescents with aggressive conduct disorder and ADDH_ a preliminary report - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">675b6af218f1fe2c234cb340e9ae6b0a1edd38749385786b0593b5f456f5a43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2135682</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Efficacy of methylphenidate among mentally retarded children with attention deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Efficacy of methylphenidate among mentally retarded children with attention deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f0a8f9ea45f2211a127fb8ed04b1fde753ee4d18d2726003b34caf303bbd6cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2387786</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Family-genetic and psychosocial risk factors in DSM-III attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Family-genetic and psychosocial risk factors in DSM-III attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ffa5d6bf3be1d4e2d1b44fa6f1245ac4d424ea5db14bd934a86b2c568c8cfe12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2074343</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Intellectual, academic, and adaptive functioning of Tourette syndrome children with and without attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Intellectual, academic, and adaptive functioning of Tourette syndrome children with and without attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">d93c46b440ae3c249f60f4415df94ae9274f74aab88e6efeaa43f947d3c3c7e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2319047</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Methylphenidate and baseball playing in ADHD children: who's on first?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Methylphenidate and baseball playing in ADHD children_ who's on first_ - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">051e409481456c178ec49ea5487634b325c2949016b85a1e35fb2d23e5437a83</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2228923</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Methylphenidate in aggressive-hyperactive boys: I. Effects on peer aggression in public school settings</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Methylphenidate in aggressive-hyperactive boys_ I. Effects on peer aggression in public school settings - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">b6ef800d54efa3d47c9f62c1f4b02e8910442dcd0756ac1b93b12c1cf45f641a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="110" customHeight="1">
+      <c r="A17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2228921</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Parent-based diagnosis of attention deficit disorder predicts a diagnosis based on teacher report</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Parent-based diagnosis of attention deficit disorder predicts a diagnosis based on teacher report - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">07e69817fb070c372660709f815d0157befb50eb0b7f9021005f16d24ab1ecb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="110" customHeight="1">
+      <c r="A18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2258453</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Possible influence of carbamazepine on plasma imipramine concentrations in children with attention deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Possible influence of carbamazepine on plasma imipramine concentrations in children with attention deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">8c1fdae328b92b0ddca983113718877183b76a26225443e7cc88775f36096515</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="110" customHeight="1">
+      <c r="A19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2196520</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Side effects of methylphenidate in children with attention deficit hyperactivity disorder: a systemic, placebo-controlled evaluation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Side effects of methylphenidate in children with attention deficit hyperactivity disorder_ a systemic, placebo-controlled evaluation - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ef6d8b034e338e72d2a54ed3031b10f22165595966626567ff8835db3d116221</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2212053</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Situational variability in boys and girls identified as ADHD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Situational variability in boys and girls identified as ADHD - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">159dfdda96e66c16692acf4f7023c63edf4a329cefeb536d7362cac6b95894b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="110" customHeight="1">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2198308</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Social judgment processes in hyperactive boys: effects of methylphenidate and comparisons with normal peers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Social judgment processes in hyperactive boys_ effects of methylphenidate and comparisons with normal peers - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">78142ba67858a930b7763d786a0523abcb54deed291a4d36056685029bf8e89f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2254504</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The adolescent outcome of hyperactive children diagnosed by research criteria: II. Academic, attentional, and neuropsychological status</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The adolescent outcome of hyperactive children diagnosed by research criteria_ II. Academic, attentional, and neuropsychological status - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1a9bd587f2aed3daeb5ae4191acd1d180d4b06a0439a8184e217ee8b3ce26758</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2235277</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The diagnostic value of cerebellar-vestibular tests in detecting learning disabilities, dyslexia, and attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The diagnostic value of cerebellar-vestibular tests in detecting learning disabilities, dyslexia, and attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ecbe1186dd50ba7d2748df6e7182d382580478faeb0b3d338519af40a2f6c7d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2273073</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The effects of behavioral parent training on families with young hyperactive children</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The effects of behavioral parent training on families with young hyperactive children - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">67fa8e220f402922cb47b1951b93a76aaa9e93067e44641f90b95d4fb84f343b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2266220</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The frequency and significance of additional self-reported psychiatric diagnoses in children with attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The frequency and significance of additional self-reported psychiatric diagnoses in children with attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">148fdc2bae935e63f4e1dd99221667bf54cf995a7a6d61ed94a2e2e43bd3847c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2342842</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The relationship between continuous performance tasks and neuropsychological tests in children with attention-deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The relationship between continuous performance tasks and neuropsychological tests in children with attention-deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">44718fa1d74d3f7e7701043ac42b03a0a8adfc2c53d22263688af463752bd3b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2288166</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Are there sex differences in the manifestation of hyperkinetic syndrome?]</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[Are there sex differences in the manifestation of hyperkinetic syndrome_] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">4d34da600d22ed8e01e957b81e86cd181494dd0495644d03852f85dbd161c3ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2346989</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Changes in the concept of minimal brain dysfunction in modern diagnostic classification and its manifestation in our theory and practice]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[Changes in the concept of minimal brain dysfunction in modern diagnostic classification and its manifestation in our theory and practice] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">eda1f1cf53ae52d2ea482c4d61a1c84d02ecabf5fab93cf902f8179b245d30e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="110" customHeight="1">
+      <c r="A29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2397543</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Preliminary study of traditional Chinese medicine treatment of minimal brain dysfunction: analysis of 100 cases]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[Preliminary study of traditional Chinese medicine treatment of minimal brain dysfunction_ analysis of 100 cases] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">45bc955d755502f0b92d2f2bba322d11c45543b468624948b512dd80419f4cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2346992</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[The importance of nonverbal motor examination methods in screening for minimal brain dysfunction]</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[The importance of nonverbal motor examination methods in screening for minimal brain dysfunction] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">a9961574979f88c2d3371365599499ac6e7111076b9a75545550443ce1a81a34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:D30"/>
 </worksheet>
 </file>
 
@@ -3024,7 +3614,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1990_8 yo.py, 58 edges, using only the four supplied PDF files in 1990 ADHD Papers. Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
+          <t xml:space="preserve">1990_8 yo.py, 58 edges, using the four supplied PDF files and 25 saved PubMed HTML abstracts in 1990 ADHD Papers. Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
         </is>
       </c>
     </row>
@@ -3084,83 +3674,107 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No exact duplicate PDF files were found in the supplied corpus.</t>
+          <t xml:space="preserve">No exact duplicate PDFs or duplicate PMID records were found. HTML pages are deduplicated by PMID; repeated sentences in an abstract are not independent findings.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="110" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: supported</t>
+          <t xml:space="preserve">html_scope</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
+          <t xml:space="preserve">HTML evidence is restricted to the main English abstract of each saved record, excluding similar/cited articles. All 25 records are dated 1990. Abstract-only limitations are retained; the side-effect abstract (PMID 2196520) is marked truncated and repeats a passage.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="110" customHeight="1">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: partially_supported</t>
+          <t xml:space="preserve">adult_scope</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
+          <t xml:space="preserve">The adult review (PMID 2251528) supplies clinical context, not a controlled treatment estimate or specific results at age 32 or 45. Pediatric findings are not transferred to adult graphs.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: contradicted</t>
+          <t xml:space="preserve">Status: supported</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
+          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: mixed_evidence</t>
+          <t xml:space="preserve">Status: partially_supported</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: insufficient_evidence</t>
+          <t xml:space="preserve">Status: contradicted</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
       <c r="A13" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Status: mixed_evidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Status: insufficient_evidence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Status: not_assessable</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="0">
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Undefined variable coding or endpoint makes the proposed direction or sign uninterpretable.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>